--- a/vlearn-app/public/quiz_excel/Day_12_Cloud Services _ Deployment/Day_12_Phan_02_22_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_12_Cloud Services _ Deployment/Day_12_Phan_02_22_Cau.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>60</v>
@@ -641,7 +641,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thời gian chờ I/O khỏi event loop và giới hạn số call đang in-flight.</t>
+          <t>Việc gọi thư viện blocking kéo dài 8 giây trực tiếp trong async handler sẽ làm nghẽn toàn bộ event loop của tiến trình; giải pháp là offload cuộc gọi đó sang thread/process pool riêng và giới hạn admission.</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -689,7 +689,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt liveness với readiness: process có thể sống nhưng chưa sẵn sàng nhận traffic.</t>
+          <t>Cần phân biệt rõ giữa liveness và readiness: Trong 18 giây khởi tạo mô hình và chỉ mục, tiến trình vẫn còn sống nhưng chưa thể nhận traffic, do đó readiness probe chỉ được phép trả về thành công sau khi init xong hoàn toàn.</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -737,7 +737,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách dữ liệu nào phải ở thiết bị, dữ liệu nào được gửi sau consent và hành vi khi offline.</t>
+          <t>Kiến trúc hybrid phù hợp với dữ liệu y tế nhạy cảm: Xử lý cục bộ tại máy người dùng để bảo đảm quyền riêng tư, chỉ gửi các tính toán nặng lên cloud model khi có sự đồng ý rõ ràng (explicit consent) của người dùng.</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -785,7 +785,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi ai có thể đọc bundle; nếu browser đọc được thì đó không còn là secret boundary.</t>
+          <t>Mọi chuỗi mã khóa nhúng trong frontend JavaScript bundle gửi tới trình duyệt đều có thể bị dịch ngược và trích xuất; giải pháp bảo mật bắt buộc là sử dụng kiến trúc Backend-for-Frontend (BFF) để giữ secret phía server.</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu bundle đã gửi tới browser, key trong đó còn là secret không?</t>
+          <t>Trình duyệt gọi trực tiếp API provider sẽ vi phạm CORS và làm lộ secret; mô hình đúng là đưa toàn bộ lời gọi qua BFF, nơi lưu trữ API key an toàn, trong khi trình duyệt xác thực với BFF bằng phiên người dùng.</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -881,7 +881,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân loại từng task theo độ nhạy, consent, capability và connectivity trước khi route.</t>
+          <t>Bảng định tuyến tác vụ dựa trên chính sách bảo mật: Tác vụ OCR nhạy cảm chạy hoàn toàn local; tác vụ marketing không nhạy cảm gửi lên cloud khi có consent; tác vụ chứa dữ liệu sinh trắc học bị cấm chuyển giao phải chạy local-only hoặc từ chối.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -929,7 +929,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu thời lượng SSE, memory, GPU và egress với giới hạn thật của runtime.</t>
+          <t>Khi ứng dụng yêu cầu duy trì kết nối SSE 15 phút, bộ nhớ 4GB và GPU chuyên dụng, môi trường serverless thông thường (giới hạn 60s) không tương thích; hệ thống bắt buộc phải chọn container runtime hỗ trợ đầy đủ các tài nguyên trên.</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60</v>
@@ -977,7 +977,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách phần provider vận hành khỏi accountability về data, policy, evaluation và khả năng rời platform.</t>
+          <t>Với đội ngũ nhỏ cần triển khai nhanh và không có nhân sự platform chuyên trách, việc sử dụng managed runtime (PaaS) là tối ưu, trong khi nhóm vẫn phải duy trì trách nhiệm giải trình về mã nguồn, dữ liệu và chính sách an toàn.</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1025,7 +1025,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra bind address và `PORT` ở runtime trước khi đổ lỗi cho CORS hay build.</t>
+          <t>Lỗi dịch vụ không nhận được lưu lượng công khai do ứng dụng bind nhầm vào `127.0.0.1:8000` thay vì biến môi trường `PORT=9000` được cấp; giải pháp là bind `0.0.0.0:$PORT` và kiểm tra lại probe ở runtime.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1073,7 +1073,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bằng chứng này được tạo trước hay sau deployment boundary?</t>
+          <t>Việc image build thành công không chứng minh được quyền truy cập; quyền truy cập tài nguyên (IAM/Workload Identity) chỉ có thể được kiểm chứng thông qua các bài probe thực tế tại môi trường runtime.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>60</v>
@@ -1121,7 +1121,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định MCP server sống cùng process local hay qua remote endpoint trước khi chọn mô hình auth.</t>
+          <t>Giao thức Model Context Protocol (MCP) chạy qua stdio giữa các tiến trình cục bộ dựa trên ranh giới tin cậy (trust boundary) của tiến trình cha; tiến trình con thừa hưởng quyền và tin cậy trực tiếp từ tiến trình gọi.</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1225,7 +1225,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định có user delegation hay không, rồi đối chiếu identity, phạm vi quyền và rotation.</t>
+          <t>Đối với dịch vụ nội bộ chạy tự động giữa các máy, mô hình xác thực tối ưu là sử dụng workload credential (như mTLS hoặc short-lived token) có phạm vi quyền hạn tối thiểu và cơ chế tự động xoay vòng định kỳ.</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1273,7 +1273,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi điều gì xảy ra với cả header thiếu lẫn header sai trước khi handler được gọi.</t>
+          <t>Cơ chế xác thực API key an toàn trong FastAPI dependency: Từ chối ngay lập tức khi thiếu hoặc sai header, sử dụng thuật toán so sánh chuỗi thời gian không đổi (`secrets.compare_digest`) để chống timing attack, và truyền identity hợp lệ xuống handler.</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1321,7 +1321,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Identity hợp lệ có mặc nhiên được phép mọi thao tác không?</t>
+          <t>Xác thực (Authentication) chỉ chứng minh danh tính của bên gọi; hệ thống bắt buộc phải có bước phân quyền (Authorization) để bảo đảm bên gọi có quyền thao tác trên tài nguyên của tenant tương ứng.</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,3,5</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1376,7 +1376,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn các trường trả lời: ai bị giới hạn, thuật toán có tham số gì và retry lúc nào.</t>
+          <t>Chính sách rate limiting đúng chuẩn multi-tenant bao gồm: (b) khóa đếm phân cấp theo tenant+tier+route để chống noisy-neighbor, (c) cấu hình dung lượng burst và tốc độ nạp (token bucket), (e) phản hồi chuẩn HTTP 429 kèm header Retry-After.</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1424,7 +1424,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp đúng điều kiện xóa timestamp rồi đếm số mốc còn lại trước khi thêm mốc mới.</t>
+          <t>Thuật toán sliding window 60s: Tại thời điểm t=60, mốc t=0 thỏa mãn điều kiện t_event &lt;= now - 60 (0 &lt;= 0) nên bị loại khỏi cửa sổ trượt, số mốc còn lại là 2 (t=20, 40) &lt; giới hạn 3; do đó request tại t=60 được cho phép.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1472,7 +1472,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính token đầu vào và đầu ra riêng theo đơn vị 1M rồi cộng hai phần.</t>
+          <t>Chi phí ước tính: (1.000 input tokens * $2 / 1.000.000) + (500 output tokens * $8 / 1.000.000) = $0,002 + $0,004 = 0,006 USD.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1520,7 +1520,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cộng phần đã dùng với chi phí ước tính cho từng tenant, không gộp hai sổ.</t>
+          <t>Quản lý ngân sách multi-tenant: Tenant A đã dùng $9/$10, request mới ước tính $2 sẽ làm vượt trần ngân sách ($11 &gt; $10) nên phải bị từ chối; trong khi sổ chi tiêu của tenant B hoàn toàn độc lập và không bị ảnh hưởng.</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1568,7 +1568,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi credential đã lộ còn được production chấp nhận hay phải vô hiệu ngay.</t>
+          <t>Khi secret bị commit nhầm lên git, dù đã xóa ở commit tiếp theo thì khóa cũ vẫn tồn tại trong lịch sử và có nguy cơ bị lộ; hành động đầu tiên bắt buộc phải là thu hồi và xoay vòng credential đó ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>60</v>
@@ -1676,7 +1676,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định bottleneck nằm ở CPU, khả năng song song, trạng thái hay quota của dependency.</t>
+          <t>Khi tiến trình xử lý stateless bị nghẽn CPU ở mức 95% trong khi ứng dụng có thể chạy song song và yêu cầu độ sẵn sàng cao, giải pháp kiến trúc tối ưu là mở rộng theo chiều ngang (horizontal scaling) kèm kiểm tra quota downstream.</t>
         </is>
       </c>
     </row>
